--- a/invoice_agent/vastra_202608.xlsx
+++ b/invoice_agent/vastra_202608.xlsx
@@ -537,7 +537,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1"/>
+  <dimension ref="A1:C2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -556,6 +556,19 @@
           <t>請求文言</t>
         </is>
       </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Vastra</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>竹田</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/invoice_agent/vastra_202608.xlsx
+++ b/invoice_agent/vastra_202608.xlsx
@@ -512,7 +512,7 @@
         <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>3467</v>
+        <v>3469</v>
       </c>
       <c r="F3" t="n">
         <v>10</v>
@@ -568,7 +568,6 @@
           <t>竹田</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/invoice_agent/vastra_202608.xlsx
+++ b/invoice_agent/vastra_202608.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,6 +461,11 @@
           <t>納品日</t>
         </is>
       </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -468,8 +473,10 @@
           <t>Vastra</t>
         </is>
       </c>
-      <c r="B2" s="1" t="n">
-        <v>46240</v>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>8/1-8/31</t>
+        </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -491,7 +498,12 @@
         </is>
       </c>
       <c r="H2" s="1" t="n">
-        <v>46240</v>
+        <v>46265</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>請求額22USDを8月6日付の日本銀行為替レート157.6719にて円転換</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -523,7 +535,7 @@
         </is>
       </c>
       <c r="H3" s="1" t="n">
-        <v>46240</v>
+        <v>46265</v>
       </c>
     </row>
   </sheetData>

--- a/invoice_agent/vastra_202608.xlsx
+++ b/invoice_agent/vastra_202608.xlsx
@@ -475,7 +475,7 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>8/1-8/31</t>
+          <t>2026年8/1-8/31</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">

--- a/invoice_agent/vastra_202608.xlsx
+++ b/invoice_agent/vastra_202608.xlsx
@@ -475,7 +475,7 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>2026年8/1-8/31</t>
+          <t>2026年8月1日-8月31日</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -524,7 +524,7 @@
         <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>3469</v>
+        <v>3468</v>
       </c>
       <c r="F3" t="n">
         <v>10</v>

--- a/invoice_agent/vastra_202608.xlsx
+++ b/invoice_agent/vastra_202608.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>請求額22USDを8月6日付の日本銀行為替レート157.6719にて円転換</t>
+          <t>Claude Pro代金20USDを8月6日付の日本銀行為替レート157.6719にて円転換（消費税10%は他の項目とあわせて別途加算）</t>
         </is>
       </c>
     </row>
@@ -524,7 +524,7 @@
         <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>3468</v>
+        <v>3153</v>
       </c>
       <c r="F3" t="n">
         <v>10</v>
